--- a/public/samples/remains/nhuakythuatcayong.xlsx
+++ b/public/samples/remains/nhuakythuatcayong.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/Kho còn lại/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAC91553-865E-0C4F-B2F6-FEB045464030}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{F3515F6B-8C50-9148-B1A0-CC0B946222EE}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="102">
   <si>
     <t>Tồn</t>
   </si>
@@ -55,6 +44,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>PLR P6NE 020</t>
@@ -333,30 +325,371 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -364,28 +697,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -434,7 +1053,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -467,26 +1086,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -519,23 +1121,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -677,29 +1262,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10EA2521-8CD0-8548-A517-C0F1919E68E2}">
-  <dimension ref="A1:K85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L85"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="4:10">
       <c r="D1" s="1"/>
-      <c r="F1" s="2"/>
-      <c r="I1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="I1" s="4"/>
       <c r="J1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -715,7 +1295,7 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G2" t="s">
@@ -724,25 +1304,28 @@
       <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -750,32 +1333,32 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I3" s="4"/>
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -783,32 +1366,32 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I4" s="4"/>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D5" s="1">
         <v>0.89</v>
@@ -816,32 +1399,32 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>0.89</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I5" s="4"/>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="3">
         <v>0.89</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -849,32 +1432,32 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I6" s="4"/>
       <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -882,32 +1465,32 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I7" s="4"/>
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -915,32 +1498,32 @@
       <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I8" s="4"/>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D9" s="1">
         <v>0.35</v>
@@ -948,32 +1531,32 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>0.35</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I9" s="4"/>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D10" s="1">
         <v>0.2</v>
@@ -981,32 +1564,32 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>0.2</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I10" s="4"/>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D11" s="1">
         <v>0.4</v>
@@ -1014,32 +1597,32 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>0.4</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I11" s="4"/>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="3">
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>26</v>
+      <c r="C12" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D12" s="1">
         <v>0.43</v>
@@ -1047,32 +1630,32 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>0.43</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I12" s="4"/>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="3">
         <v>0.43</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D13" s="1">
         <v>0.37</v>
@@ -1080,32 +1663,32 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>0.37</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I13" s="4"/>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="3">
         <v>0.37</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="4" t="s">
         <v>34</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="1">
         <v>0.315</v>
@@ -1113,32 +1696,32 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>0.315</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I14" s="4"/>
       <c r="J14">
         <v>0</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -1146,32 +1729,32 @@
       <c r="E15">
         <v>19</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I15" s="4"/>
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -1179,32 +1762,32 @@
       <c r="E16">
         <v>17</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I16" s="4"/>
       <c r="J16">
         <v>15</v>
       </c>
-      <c r="K16" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K16" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -1212,32 +1795,32 @@
       <c r="E17">
         <v>5</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I17" s="4"/>
       <c r="J17">
         <v>5</v>
       </c>
-      <c r="K17" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -1245,32 +1828,32 @@
       <c r="E18">
         <v>34</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I18" s="4"/>
       <c r="J18">
         <v>34</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="D19" s="1">
         <v>0.6</v>
@@ -1278,32 +1861,32 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>0.6</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I19" s="4"/>
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D20" s="1">
         <v>0.6</v>
@@ -1311,32 +1894,32 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>0.6</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I20" s="4"/>
       <c r="J20">
         <v>1</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>43</v>
+        <v>34</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D21" s="1">
         <v>0.61</v>
@@ -1344,32 +1927,32 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>0.61</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I21" s="4"/>
       <c r="J21">
         <v>1</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="3">
         <v>0.61</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -1377,32 +1960,32 @@
       <c r="E22">
         <v>4</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I22" s="4"/>
       <c r="J22">
         <v>4</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="D23" s="1">
         <v>0.98</v>
@@ -1410,65 +1993,65 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>0.98</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I23" s="4"/>
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.052</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.052</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="1">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="3"/>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2">
-        <v>5.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" s="1">
         <v>0.48</v>
@@ -1476,98 +2059,98 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>0.48</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I25" s="4"/>
       <c r="J25">
         <v>1</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25" s="3">
         <v>0.48</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.049</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.049</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="1">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2">
-        <v>4.9000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D27" s="1">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27" s="2">
-        <v>3.7999999999999999E-2</v>
+      <c r="F27" s="3">
+        <v>0.038</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I27" s="4"/>
       <c r="J27">
         <v>1</v>
       </c>
-      <c r="K27" s="2">
-        <v>3.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="4" t="s">
         <v>53</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -1575,32 +2158,32 @@
       <c r="E28">
         <v>2</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I28" s="4"/>
       <c r="J28">
         <v>2</v>
       </c>
-      <c r="K28" s="2">
+      <c r="K28" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -1608,32 +2191,32 @@
       <c r="E29">
         <v>2</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>6</v>
       </c>
       <c r="G29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I29" s="4"/>
       <c r="J29">
         <v>2</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -1641,32 +2224,32 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I30" s="4"/>
       <c r="J30">
         <v>1</v>
       </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
@@ -1674,32 +2257,32 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I31" s="4"/>
       <c r="J31">
         <v>1</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D32" s="1">
         <v>0.215</v>
@@ -1707,32 +2290,32 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>0.215</v>
       </c>
       <c r="G32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I32" s="4"/>
       <c r="J32">
         <v>1</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="3">
         <v>0.215</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
@@ -1740,32 +2323,32 @@
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I33" s="4"/>
       <c r="J33">
         <v>1</v>
       </c>
-      <c r="K33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -1773,32 +2356,32 @@
       <c r="E34">
         <v>5</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I34" s="4"/>
       <c r="J34">
         <v>5</v>
       </c>
-      <c r="K34" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
@@ -1806,32 +2389,32 @@
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I35" s="4"/>
       <c r="J35">
         <v>1</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K35" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -1839,32 +2422,32 @@
       <c r="E36">
         <v>1</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I36" s="4"/>
       <c r="J36">
         <v>1</v>
       </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K36" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
@@ -1872,32 +2455,32 @@
       <c r="E37">
         <v>1</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="3">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I37" s="4"/>
       <c r="J37">
         <v>1</v>
       </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K37" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>41</v>
+        <v>53</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -1905,32 +2488,32 @@
       <c r="E38">
         <v>6</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I38" s="4"/>
       <c r="J38">
         <v>6</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>41</v>
+        <v>53</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -1938,32 +2521,32 @@
       <c r="E39">
         <v>1</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="3">
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I39" s="4"/>
       <c r="J39">
         <v>1</v>
       </c>
-      <c r="K39" s="2">
+      <c r="K39" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>18</v>
+        <v>64</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -1971,32 +2554,32 @@
       <c r="E40">
         <v>3</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I40" s="4"/>
       <c r="J40">
         <v>3</v>
       </c>
-      <c r="K40" s="2">
+      <c r="K40" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>18</v>
+        <v>64</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D41" s="1">
         <v>2.31</v>
@@ -2004,32 +2587,32 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="3">
         <v>2.31</v>
       </c>
       <c r="G41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>14</v>
-      </c>
-      <c r="I41" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I41" s="4"/>
       <c r="J41">
         <v>0</v>
       </c>
-      <c r="K41" s="2">
+      <c r="K41" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>18</v>
+        <v>64</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D42" s="1">
         <v>0.02</v>
@@ -2037,32 +2620,32 @@
       <c r="E42">
         <v>1</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>0.02</v>
       </c>
       <c r="G42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
-      </c>
-      <c r="I42" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I42" s="4"/>
       <c r="J42">
         <v>1</v>
       </c>
-      <c r="K42" s="2">
+      <c r="K42" s="3">
         <v>0.02</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" t="s">
         <v>64</v>
       </c>
-      <c r="B43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>20</v>
+      <c r="C43" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
@@ -2070,32 +2653,32 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I43" s="4"/>
       <c r="J43">
         <v>0</v>
       </c>
-      <c r="K43" s="2">
+      <c r="K43" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" t="s">
         <v>64</v>
       </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>20</v>
+      <c r="C44" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D44" s="1">
         <v>0.7</v>
@@ -2103,32 +2686,32 @@
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="3">
         <v>0.7</v>
       </c>
       <c r="G44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I44" s="4"/>
       <c r="J44">
         <v>0</v>
       </c>
-      <c r="K44" s="2">
+      <c r="K44" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D45" s="1">
         <v>0.125</v>
@@ -2136,32 +2719,32 @@
       <c r="E45">
         <v>42</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <v>5.25</v>
       </c>
       <c r="G45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I45" s="4"/>
       <c r="J45">
         <v>42</v>
       </c>
-      <c r="K45" s="2">
+      <c r="K45" s="3">
         <v>5.25</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="4" t="s">
         <v>68</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
@@ -2169,32 +2752,32 @@
       <c r="E46">
         <v>3</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="3">
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>14</v>
-      </c>
-      <c r="I46" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I46" s="4"/>
       <c r="J46">
         <v>3</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K46" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>16</v>
+        <v>68</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -2202,32 +2785,32 @@
       <c r="E47">
         <v>2</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="3">
         <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I47" s="4"/>
       <c r="J47">
         <v>2</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K47" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="4" t="s">
         <v>71</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="D48" s="1">
         <v>0.91</v>
@@ -2235,32 +2818,32 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="3">
         <v>0.91</v>
       </c>
       <c r="G48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I48" s="4"/>
       <c r="J48">
         <v>1</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K48" s="3">
         <v>0.91</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
-      </c>
-      <c r="C49" s="4" t="s">
         <v>74</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -2268,65 +2851,65 @@
       <c r="E49">
         <v>228</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="3">
         <v>684</v>
       </c>
       <c r="G49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I49" s="4"/>
       <c r="J49">
         <v>228</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K49" s="3">
         <v>684</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B50" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.225</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0.225</v>
+      </c>
+      <c r="G50" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50" s="3">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
         <v>73</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="G50" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50" s="3"/>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50" s="2">
-        <v>0.22500000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>72</v>
-      </c>
       <c r="B51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>57</v>
+        <v>74</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D51" s="1">
         <v>0.54</v>
@@ -2334,32 +2917,32 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="3">
         <v>0.54</v>
       </c>
       <c r="G51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I51" s="4"/>
       <c r="J51">
         <v>1</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="3">
         <v>0.54</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>57</v>
+        <v>74</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D52" s="1">
         <v>0.22</v>
@@ -2367,32 +2950,32 @@
       <c r="E52">
         <v>1</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="3">
         <v>0.22</v>
       </c>
       <c r="G52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I52" s="4"/>
       <c r="J52">
         <v>1</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52" s="3">
         <v>0.22</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" s="4" t="s">
         <v>78</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
@@ -2400,32 +2983,32 @@
       <c r="E53">
         <v>140</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="3">
         <v>420</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I53" s="4"/>
       <c r="J53">
         <v>140</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K53" s="3">
         <v>420</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" s="4" t="s">
         <v>78</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="D54" s="1">
         <v>1.6</v>
@@ -2433,32 +3016,32 @@
       <c r="E54">
         <v>1</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="3">
         <v>1.6</v>
       </c>
       <c r="G54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I54" s="4"/>
       <c r="J54">
         <v>1</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K54" s="3">
         <v>1.6</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>22</v>
+        <v>81</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
@@ -2466,32 +3049,32 @@
       <c r="E55">
         <v>22</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="3">
         <v>22</v>
       </c>
       <c r="G55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I55" s="4"/>
       <c r="J55">
         <v>0</v>
       </c>
-      <c r="K55" s="2">
+      <c r="K55" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>22</v>
+        <v>81</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D56" s="1">
         <v>0.33</v>
@@ -2499,32 +3082,32 @@
       <c r="E56">
         <v>1</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="3">
         <v>0.33</v>
       </c>
       <c r="G56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I56" s="4"/>
       <c r="J56">
         <v>0</v>
       </c>
-      <c r="K56" s="2">
+      <c r="K56" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>80</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>22</v>
+        <v>81</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D57" s="1">
         <v>0.16</v>
@@ -2532,32 +3115,32 @@
       <c r="E57">
         <v>1</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="3">
         <v>0.16</v>
       </c>
       <c r="G57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I57" s="4"/>
       <c r="J57">
         <v>0</v>
       </c>
-      <c r="K57" s="2">
+      <c r="K57" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>22</v>
+        <v>81</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
@@ -2565,69 +3148,69 @@
       <c r="E58">
         <v>50</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="3">
         <v>50</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" s="3">
+        <v>15</v>
+      </c>
+      <c r="I58" s="4">
         <v>44391</v>
       </c>
       <c r="J58">
         <v>39</v>
       </c>
-      <c r="K58" s="2">
+      <c r="K58" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D59" s="1">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
-      <c r="F59" s="2">
-        <v>0.20499999999999999</v>
+      <c r="F59" s="3">
+        <v>0.205</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H59">
         <v>2101511</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="4">
         <v>44391</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
-      <c r="K59" s="2">
+      <c r="K59" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D60" s="1">
         <v>0.75</v>
@@ -2635,34 +3218,34 @@
       <c r="E60">
         <v>1</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="3">
         <v>0.75</v>
       </c>
       <c r="G60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H60">
         <v>2101768</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="4">
         <v>44449</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
-      <c r="K60" s="2">
+      <c r="K60" s="3">
         <v>0.75</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D61" s="1">
         <v>0.6</v>
@@ -2670,69 +3253,69 @@
       <c r="E61">
         <v>1</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="3">
         <v>0.6</v>
       </c>
       <c r="G61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H61">
         <v>2101865</v>
       </c>
-      <c r="I61" s="3">
+      <c r="I61" s="4">
         <v>44468</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
-      <c r="K61" s="2">
+      <c r="K61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>18</v>
+        <v>64</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D62" s="1">
-        <v>2.2599999999999998</v>
+        <v>2.26</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
-      <c r="F62" s="2">
-        <v>2.2599999999999998</v>
+      <c r="F62" s="3">
+        <v>2.26</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H62">
         <v>2102388</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="4">
         <v>44534</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
-      <c r="K62" s="2">
+      <c r="K62" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>84</v>
+        <v>34</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
@@ -2740,34 +3323,34 @@
       <c r="E63">
         <v>50</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="3">
         <v>50</v>
       </c>
       <c r="G63" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" s="3">
+        <v>15</v>
+      </c>
+      <c r="I63" s="4">
         <v>44588</v>
       </c>
       <c r="J63">
         <v>4</v>
       </c>
-      <c r="K63" s="2">
+      <c r="K63" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" s="4" t="s">
         <v>34</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -2775,34 +3358,34 @@
       <c r="E64">
         <v>50</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="3">
         <v>50</v>
       </c>
       <c r="G64" t="s">
+        <v>86</v>
+      </c>
+      <c r="H64" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="4">
+        <v>44588</v>
+      </c>
+      <c r="J64">
+        <v>14</v>
+      </c>
+      <c r="K64" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="H64" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" s="3">
-        <v>44588</v>
-      </c>
-      <c r="J64">
-        <v>14</v>
-      </c>
-      <c r="K64" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="D65" s="1">
         <v>0.5</v>
@@ -2810,34 +3393,34 @@
       <c r="E65">
         <v>1</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="3">
         <v>0.5</v>
       </c>
       <c r="G65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H65">
         <v>2200083</v>
       </c>
-      <c r="I65" s="3">
+      <c r="I65" s="4">
         <v>44573</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
-      <c r="K65" s="2">
+      <c r="K65" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
-      </c>
-      <c r="C66" s="4" t="s">
         <v>88</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
@@ -2845,34 +3428,34 @@
       <c r="E66">
         <v>20</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="3">
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s">
-        <v>14</v>
-      </c>
-      <c r="I66" s="3">
+        <v>15</v>
+      </c>
+      <c r="I66" s="4">
         <v>44716</v>
       </c>
       <c r="J66">
         <v>19</v>
       </c>
-      <c r="K66" s="2">
+      <c r="K66" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="D67" s="1">
         <v>1</v>
@@ -2880,34 +3463,34 @@
       <c r="E67">
         <v>20</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="3">
         <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="3">
+        <v>15</v>
+      </c>
+      <c r="I67" s="4">
         <v>44716</v>
       </c>
       <c r="J67">
         <v>19</v>
       </c>
-      <c r="K67" s="2">
+      <c r="K67" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -2915,34 +3498,34 @@
       <c r="E68">
         <v>20</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="3">
         <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
-      </c>
-      <c r="I68" s="3">
+        <v>15</v>
+      </c>
+      <c r="I68" s="4">
         <v>44716</v>
       </c>
       <c r="J68">
         <v>19</v>
       </c>
-      <c r="K68" s="2">
+      <c r="K68" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
@@ -2950,34 +3533,34 @@
       <c r="E69">
         <v>20</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="3">
         <v>20</v>
       </c>
       <c r="G69" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" s="3">
+        <v>15</v>
+      </c>
+      <c r="I69" s="4">
         <v>44716</v>
       </c>
       <c r="J69">
         <v>19</v>
       </c>
-      <c r="K69" s="2">
+      <c r="K69" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
-      </c>
-      <c r="C70" s="4" t="s">
         <v>88</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="D70" s="1">
         <v>0.82</v>
@@ -2985,34 +3568,34 @@
       <c r="E70">
         <v>1</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="3">
         <v>0.82</v>
       </c>
       <c r="G70" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H70">
         <v>2201395</v>
       </c>
-      <c r="I70" s="3">
+      <c r="I70" s="4">
         <v>44721</v>
       </c>
       <c r="J70">
         <v>1</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70" s="3">
         <v>0.82</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="D71" s="1">
         <v>0.85</v>
@@ -3020,69 +3603,69 @@
       <c r="E71">
         <v>1</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="3">
         <v>0.85</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H71">
         <v>2201395</v>
       </c>
-      <c r="I71" s="3">
+      <c r="I71" s="4">
         <v>44721</v>
       </c>
       <c r="J71">
         <v>1</v>
       </c>
-      <c r="K71" s="2">
+      <c r="K71" s="3">
         <v>0.85</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="D72" s="1">
-        <v>0.67500000000000004</v>
+        <v>0.675</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
-      <c r="F72" s="2">
-        <v>0.67500000000000004</v>
+      <c r="F72" s="3">
+        <v>0.675</v>
       </c>
       <c r="G72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H72">
         <v>2201395</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="4">
         <v>44721</v>
       </c>
       <c r="J72">
         <v>1</v>
       </c>
-      <c r="K72" s="2">
-        <v>0.67500000000000004</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="D73" s="1">
         <v>0.92</v>
@@ -3090,69 +3673,69 @@
       <c r="E73">
         <v>1</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="3">
         <v>0.92</v>
       </c>
       <c r="G73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H73">
         <v>2201395</v>
       </c>
-      <c r="I73" s="3">
+      <c r="I73" s="4">
         <v>44721</v>
       </c>
       <c r="J73">
         <v>1</v>
       </c>
-      <c r="K73" s="2">
+      <c r="K73" s="3">
         <v>0.92</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>18</v>
+        <v>64</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D74" s="1">
-        <v>2.0249999999999999</v>
+        <v>2.025</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
-      <c r="F74" s="2">
-        <v>2.0249999999999999</v>
+      <c r="F74" s="3">
+        <v>2.025</v>
       </c>
       <c r="G74" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H74">
         <v>2201824</v>
       </c>
-      <c r="I74" s="3">
+      <c r="I74" s="4">
         <v>44769</v>
       </c>
       <c r="J74">
         <v>1</v>
       </c>
-      <c r="K74" s="2">
-        <v>2.0249999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>2.025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -3160,32 +3743,32 @@
       <c r="E75">
         <v>18</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="3">
         <v>18</v>
       </c>
       <c r="G75" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s">
-        <v>97</v>
-      </c>
-      <c r="I75" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I75" s="4"/>
       <c r="J75">
         <v>17</v>
       </c>
-      <c r="K75" s="2">
+      <c r="K75" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D76" s="1">
         <v>0.86</v>
@@ -3193,32 +3776,32 @@
       <c r="E76">
         <v>1</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="3">
         <v>0.86</v>
       </c>
       <c r="G76" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s">
+        <v>98</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76" s="3">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="I76" s="3"/>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="K76" s="2">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" t="s">
-        <v>87</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D77" s="1">
         <v>0.82</v>
@@ -3226,32 +3809,32 @@
       <c r="E77">
         <v>1</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="3">
         <v>0.82</v>
       </c>
       <c r="G77" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s">
-        <v>97</v>
-      </c>
-      <c r="I77" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I77" s="4"/>
       <c r="J77">
         <v>1</v>
       </c>
-      <c r="K77" s="2">
+      <c r="K77" s="3">
         <v>0.82</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D78" s="1">
         <v>1</v>
@@ -3259,32 +3842,32 @@
       <c r="E78">
         <v>18</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="3">
         <v>18</v>
       </c>
       <c r="G78" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s">
-        <v>97</v>
-      </c>
-      <c r="I78" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I78" s="4"/>
       <c r="J78">
         <v>17</v>
       </c>
-      <c r="K78" s="2">
+      <c r="K78" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D79" s="1">
         <v>0.85</v>
@@ -3292,32 +3875,32 @@
       <c r="E79">
         <v>1</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="3">
         <v>0.85</v>
       </c>
       <c r="G79" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s">
-        <v>97</v>
-      </c>
-      <c r="I79" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I79" s="4"/>
       <c r="J79">
         <v>1</v>
       </c>
-      <c r="K79" s="2">
+      <c r="K79" s="3">
         <v>0.85</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D80" s="1">
         <v>0.81</v>
@@ -3325,32 +3908,32 @@
       <c r="E80">
         <v>1</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="3">
         <v>0.81</v>
       </c>
       <c r="G80" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s">
-        <v>97</v>
-      </c>
-      <c r="I80" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I80" s="4"/>
       <c r="J80">
         <v>1</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80" s="3">
         <v>0.81</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="D81" s="1">
         <v>1</v>
@@ -3358,65 +3941,65 @@
       <c r="E81">
         <v>19</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="3">
         <v>19</v>
       </c>
       <c r="G81" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s">
-        <v>97</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I81" s="4"/>
       <c r="J81">
         <v>18</v>
       </c>
-      <c r="K81" s="2">
+      <c r="K81" s="3">
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="D82" s="1">
-        <v>0.67500000000000004</v>
+        <v>0.675</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
-      <c r="F82" s="2">
-        <v>0.67500000000000004</v>
+      <c r="F82" s="3">
+        <v>0.675</v>
       </c>
       <c r="G82" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s">
-        <v>97</v>
-      </c>
-      <c r="I82" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I82" s="4"/>
       <c r="J82">
         <v>1</v>
       </c>
-      <c r="K82" s="2">
-        <v>0.67500000000000004</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K82" s="3">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -3424,32 +4007,32 @@
       <c r="E83">
         <v>19</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="3">
         <v>19</v>
       </c>
       <c r="G83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s">
-        <v>97</v>
-      </c>
-      <c r="I83" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I83" s="4"/>
       <c r="J83">
         <v>18</v>
       </c>
-      <c r="K83" s="2">
+      <c r="K83" s="3">
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>87</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="D84" s="1">
         <v>0.92</v>
@@ -3457,32 +4040,32 @@
       <c r="E84">
         <v>1</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="3">
         <v>0.92</v>
       </c>
       <c r="G84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s">
-        <v>97</v>
-      </c>
-      <c r="I84" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I84" s="4"/>
       <c r="J84">
         <v>1</v>
       </c>
-      <c r="K84" s="2">
+      <c r="K84" s="3">
         <v>0.92</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>33</v>
-      </c>
-      <c r="C85" s="2" t="s">
         <v>34</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="D85" s="1">
         <v>0.3</v>
@@ -3490,26 +4073,27 @@
       <c r="E85">
         <v>1</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="3">
         <v>0.3</v>
       </c>
       <c r="G85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H85">
         <v>2202711</v>
       </c>
-      <c r="I85" s="3">
+      <c r="I85" s="4">
         <v>44855</v>
       </c>
       <c r="J85">
         <v>1</v>
       </c>
-      <c r="K85" s="2">
+      <c r="K85" s="3">
         <v>0.3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>